--- a/labeled/Add_Eating/July/multi_seed_results/seed_505/predictions.xlsx
+++ b/labeled/Add_Eating/July/multi_seed_results/seed_505/predictions.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B146"/>
+  <dimension ref="A1:B94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -442,618 +442,618 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>40</v>
+        <v>20.17629814147949</v>
       </c>
       <c r="B2" t="n">
-        <v>39.16904067993164</v>
+        <v>21.3978443145752</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>22.9187068939209</v>
+        <v>32.22331237792969</v>
       </c>
       <c r="B3" t="n">
-        <v>28.09195709228516</v>
+        <v>28.96514320373535</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>85.69999694824219</v>
+        <v>11.33333301544189</v>
       </c>
       <c r="B4" t="n">
-        <v>85.58621215820312</v>
+        <v>14.92287826538086</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>10.4761905670166</v>
+        <v>30.55827713012695</v>
       </c>
       <c r="B5" t="n">
-        <v>27.65836715698242</v>
+        <v>21.02059745788574</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>20.38095283508301</v>
+        <v>43.79999923706055</v>
       </c>
       <c r="B6" t="n">
-        <v>19.75293159484863</v>
+        <v>49.83016204833984</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>60</v>
+        <v>32.41919708251953</v>
       </c>
       <c r="B7" t="n">
-        <v>53.29429626464844</v>
+        <v>37.89067840576172</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>26.44466209411621</v>
+        <v>27.29999923706055</v>
       </c>
       <c r="B8" t="n">
-        <v>30.38520050048828</v>
+        <v>18.02346229553223</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>18.70000076293945</v>
+        <v>33.63095092773438</v>
       </c>
       <c r="B9" t="n">
-        <v>18.21014022827148</v>
+        <v>20.57131767272949</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>97.94319152832031</v>
+        <v>28.7952995300293</v>
       </c>
       <c r="B10" t="n">
-        <v>98.19888305664062</v>
+        <v>27.91109848022461</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>40</v>
+        <v>26.40394020080566</v>
       </c>
       <c r="B11" t="n">
-        <v>30.1643123626709</v>
+        <v>9.740922927856445</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>36.29999923706055</v>
+        <v>17.70000076293945</v>
       </c>
       <c r="B12" t="n">
-        <v>34.08210754394531</v>
+        <v>28.22385025024414</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>22.09523773193359</v>
+        <v>35.20000076293945</v>
       </c>
       <c r="B13" t="n">
-        <v>31.15716171264648</v>
+        <v>30.07655906677246</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>27.18253898620605</v>
+        <v>21.89999961853027</v>
       </c>
       <c r="B14" t="n">
-        <v>23.13236236572266</v>
+        <v>16.62990760803223</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>27.90476226806641</v>
+        <v>18</v>
       </c>
       <c r="B15" t="n">
-        <v>25.19943046569824</v>
+        <v>20.85326957702637</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>27.32615089416504</v>
+        <v>16.5714282989502</v>
       </c>
       <c r="B16" t="n">
-        <v>26.19200706481934</v>
+        <v>14.6163501739502</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>40.09523773193359</v>
+        <v>6.547618865966797</v>
       </c>
       <c r="B17" t="n">
-        <v>26.12519264221191</v>
+        <v>7.736173152923584</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>20.33730125427246</v>
+        <v>24.89999961853027</v>
       </c>
       <c r="B18" t="n">
-        <v>21.88103866577148</v>
+        <v>32.17413330078125</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>17.70000076293945</v>
+        <v>10.47992134094238</v>
       </c>
       <c r="B19" t="n">
-        <v>22.38094329833984</v>
+        <v>13.04986572265625</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>19.09892272949219</v>
+        <v>18.19047546386719</v>
       </c>
       <c r="B20" t="n">
-        <v>23.56739044189453</v>
+        <v>17.16152954101562</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>18.51126289367676</v>
+        <v>8.666666984558105</v>
       </c>
       <c r="B21" t="n">
-        <v>18.47356796264648</v>
+        <v>21.45444297790527</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>40</v>
+        <v>23.01665115356445</v>
       </c>
       <c r="B22" t="n">
-        <v>39.16904067993164</v>
+        <v>30.87611961364746</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>11.2380952835083</v>
+        <v>10.7619047164917</v>
       </c>
       <c r="B23" t="n">
-        <v>17.87212371826172</v>
+        <v>17.08824348449707</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>12.5</v>
+        <v>57.78648376464844</v>
       </c>
       <c r="B24" t="n">
-        <v>12.10221576690674</v>
+        <v>39.0489616394043</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>60</v>
+        <v>29.10000038146973</v>
       </c>
       <c r="B25" t="n">
-        <v>49.85964584350586</v>
+        <v>26.6054859161377</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>36.23898315429688</v>
+        <v>45</v>
       </c>
       <c r="B26" t="n">
-        <v>37.28806686401367</v>
+        <v>38.95005416870117</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>24.58374214172363</v>
+        <v>14.19999980926514</v>
       </c>
       <c r="B27" t="n">
-        <v>29.10256767272949</v>
+        <v>17.90619087219238</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>20.33730125427246</v>
+        <v>23.5238094329834</v>
       </c>
       <c r="B28" t="n">
-        <v>18.15102386474609</v>
+        <v>26.19036865234375</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>19.58863830566406</v>
+        <v>25.39999961853027</v>
       </c>
       <c r="B29" t="n">
-        <v>35.06578826904297</v>
+        <v>16.5544319152832</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>58</v>
+        <v>58.40000152587891</v>
       </c>
       <c r="B30" t="n">
-        <v>59.27699279785156</v>
+        <v>37.72856903076172</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>11.65524005889893</v>
+        <v>8.952381134033203</v>
       </c>
       <c r="B31" t="n">
-        <v>19.46665382385254</v>
+        <v>16.44075393676758</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>27.81586647033691</v>
+        <v>6.660137176513672</v>
       </c>
       <c r="B32" t="n">
-        <v>21.31435585021973</v>
+        <v>9.726356506347656</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>17.26190567016602</v>
+        <v>25.79999923706055</v>
       </c>
       <c r="B33" t="n">
-        <v>22.78930282592773</v>
+        <v>23.96027565002441</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>13.10000038146973</v>
+        <v>54.29999923706055</v>
       </c>
       <c r="B34" t="n">
-        <v>14.1387882232666</v>
+        <v>58.19601440429688</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>6.0724778175354</v>
+        <v>14.18650817871094</v>
       </c>
       <c r="B35" t="n">
-        <v>17.52369689941406</v>
+        <v>18.26279640197754</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>19.79999923706055</v>
+        <v>69.63761138916016</v>
       </c>
       <c r="B36" t="n">
-        <v>18.47074317932129</v>
+        <v>67.26706695556641</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>19.84127044677734</v>
+        <v>24.68168449401855</v>
       </c>
       <c r="B37" t="n">
-        <v>25.04225158691406</v>
+        <v>21.96961402893066</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>100</v>
+        <v>24.39999961853027</v>
       </c>
       <c r="B38" t="n">
-        <v>82.74571228027344</v>
+        <v>30.91845703125</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>91.5</v>
+        <v>21.05778694152832</v>
       </c>
       <c r="B39" t="n">
-        <v>90.27391815185547</v>
+        <v>21.71211051940918</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>40</v>
+        <v>20.83333396911621</v>
       </c>
       <c r="B40" t="n">
-        <v>35.72237014770508</v>
+        <v>21.57674407958984</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>81</v>
+        <v>23.70000076293945</v>
       </c>
       <c r="B41" t="n">
-        <v>78.26290130615234</v>
+        <v>31.7739372253418</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>68.85713958740234</v>
+        <v>21.74338912963867</v>
       </c>
       <c r="B42" t="n">
-        <v>63.49165725708008</v>
+        <v>19.40457344055176</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>20.33730125427246</v>
+        <v>12.30158710479736</v>
       </c>
       <c r="B43" t="n">
-        <v>21.88103866577148</v>
+        <v>14.83359718322754</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="B44" t="n">
-        <v>78.28827667236328</v>
+        <v>57.84183120727539</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>25.79365158081055</v>
+        <v>25.5</v>
       </c>
       <c r="B45" t="n">
-        <v>17.41699409484863</v>
+        <v>25.52246284484863</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>24.00793647766113</v>
+        <v>13.32027435302734</v>
       </c>
       <c r="B46" t="n">
-        <v>23.19329643249512</v>
+        <v>18.32809257507324</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>31</v>
+        <v>35.29999923706055</v>
       </c>
       <c r="B47" t="n">
-        <v>27.86735725402832</v>
+        <v>34.04782104492188</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>81</v>
+        <v>30.66666603088379</v>
       </c>
       <c r="B48" t="n">
-        <v>78.26290130615234</v>
+        <v>26.92769241333008</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>17.36111068725586</v>
+        <v>12.53672885894775</v>
       </c>
       <c r="B49" t="n">
-        <v>23.60426712036133</v>
+        <v>17.16764068603516</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>80</v>
+        <v>14.58333301544189</v>
       </c>
       <c r="B50" t="n">
-        <v>73.59597015380859</v>
+        <v>11.67724418640137</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>39.17727661132812</v>
+        <v>24.50396919250488</v>
       </c>
       <c r="B51" t="n">
-        <v>33.06288528442383</v>
+        <v>26.60508346557617</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>78.35455322265625</v>
+        <v>18.70000076293945</v>
       </c>
       <c r="B52" t="n">
-        <v>75.57651519775391</v>
+        <v>16.75455093383789</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>15.46798038482666</v>
+        <v>16.5714282989502</v>
       </c>
       <c r="B53" t="n">
-        <v>15.28472805023193</v>
+        <v>12.23527908325195</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>27.71792411804199</v>
+        <v>13.10000038146973</v>
       </c>
       <c r="B54" t="n">
-        <v>24.23316383361816</v>
+        <v>18.36138343811035</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>17.70000076293945</v>
+        <v>46.70000076293945</v>
       </c>
       <c r="B55" t="n">
-        <v>22.38094329833984</v>
+        <v>18.59055709838867</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>68.85713958740234</v>
+        <v>19.5</v>
       </c>
       <c r="B56" t="n">
-        <v>63.49165725708008</v>
+        <v>14.79817390441895</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>29.39999961853027</v>
+        <v>25.75905990600586</v>
       </c>
       <c r="B57" t="n">
-        <v>28.43615341186523</v>
+        <v>27.49352073669434</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>22.33104705810547</v>
+        <v>23.5</v>
       </c>
       <c r="B58" t="n">
-        <v>18.43946266174316</v>
+        <v>16.0380916595459</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>8.630952835083008</v>
+        <v>57.09999847412109</v>
       </c>
       <c r="B59" t="n">
-        <v>12.30843544006348</v>
+        <v>68.00173187255859</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>9.142857551574707</v>
+        <v>70.47618865966797</v>
       </c>
       <c r="B60" t="n">
-        <v>20.17044830322266</v>
+        <v>58.98524856567383</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>14.1304349899292</v>
+        <v>16.38095283508301</v>
       </c>
       <c r="B61" t="n">
-        <v>12.01351356506348</v>
+        <v>26.29106712341309</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>24.10000038146973</v>
+        <v>31.63565063476562</v>
       </c>
       <c r="B62" t="n">
-        <v>23.3097095489502</v>
+        <v>27.28661155700684</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>18.51126289367676</v>
+        <v>57</v>
       </c>
       <c r="B63" t="n">
-        <v>18.47356796264648</v>
+        <v>63.44227600097656</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>33.39862823486328</v>
+        <v>14.20176315307617</v>
       </c>
       <c r="B64" t="n">
-        <v>22.6586971282959</v>
+        <v>20.64267921447754</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>9.06403923034668</v>
+        <v>19.09892272949219</v>
       </c>
       <c r="B65" t="n">
-        <v>8.191864013671875</v>
+        <v>23.96364974975586</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>42.19047546386719</v>
+        <v>22.09523773193359</v>
       </c>
       <c r="B66" t="n">
-        <v>24.14770317077637</v>
+        <v>25.71368408203125</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>18.31537628173828</v>
+        <v>19.84127044677734</v>
       </c>
       <c r="B67" t="n">
-        <v>15.34583854675293</v>
+        <v>37.56105804443359</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>18.84920692443848</v>
+        <v>22.51984214782715</v>
       </c>
       <c r="B68" t="n">
-        <v>29.31973648071289</v>
+        <v>16.24426078796387</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>79.36508178710938</v>
+        <v>35.5</v>
       </c>
       <c r="B69" t="n">
-        <v>77.18216705322266</v>
+        <v>30.76962852478027</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>33.70000076293945</v>
+        <v>33</v>
       </c>
       <c r="B70" t="n">
-        <v>27.91191101074219</v>
+        <v>45.06960296630859</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>11.65524005889893</v>
+        <v>12.5</v>
       </c>
       <c r="B71" t="n">
-        <v>19.46665382385254</v>
+        <v>10.32497215270996</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>141.6000061035156</v>
+        <v>29.60000038146973</v>
       </c>
       <c r="B72" t="n">
-        <v>141.2825469970703</v>
+        <v>26.03364753723145</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>13.22233104705811</v>
+        <v>32.85714340209961</v>
       </c>
       <c r="B73" t="n">
-        <v>17.06057357788086</v>
+        <v>33.31298828125</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>20.80867767333984</v>
+        <v>36</v>
       </c>
       <c r="B74" t="n">
-        <v>14.9269323348999</v>
+        <v>21.39062118530273</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>32.22331237792969</v>
+        <v>7.737512111663818</v>
       </c>
       <c r="B75" t="n">
-        <v>31.80102920532227</v>
+        <v>11.43132591247559</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>8.380952835083008</v>
+        <v>15.083251953125</v>
       </c>
       <c r="B76" t="n">
-        <v>34.55740356445312</v>
+        <v>17.18888473510742</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>43.79999923706055</v>
+        <v>28.10000038146973</v>
       </c>
       <c r="B77" t="n">
-        <v>39.75958633422852</v>
+        <v>33.03666687011719</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>16.5714282989502</v>
+        <v>12.74703598022461</v>
       </c>
       <c r="B78" t="n">
-        <v>15.3988151550293</v>
+        <v>12.76948165893555</v>
       </c>
     </row>
     <row r="79">
@@ -1061,543 +1061,127 @@
         <v>70.80000305175781</v>
       </c>
       <c r="B79" t="n">
-        <v>69.98377990722656</v>
+        <v>62.68802261352539</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>28.7952995300293</v>
+        <v>9.990205764770508</v>
       </c>
       <c r="B80" t="n">
-        <v>28.30174255371094</v>
+        <v>10.38118743896484</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>35.20000076293945</v>
+        <v>27.90476226806641</v>
       </c>
       <c r="B81" t="n">
-        <v>30.87546920776367</v>
+        <v>25.29770469665527</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>12.74703598022461</v>
+        <v>11.8095235824585</v>
       </c>
       <c r="B82" t="n">
-        <v>16.27081489562988</v>
+        <v>16.80783081054688</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>10.47992134094238</v>
+        <v>9.486166000366211</v>
       </c>
       <c r="B83" t="n">
-        <v>15.12986278533936</v>
+        <v>6.350601673126221</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>30.19047546386719</v>
+        <v>73.5</v>
       </c>
       <c r="B84" t="n">
-        <v>24.00968933105469</v>
+        <v>63.55595016479492</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>14.58333301544189</v>
+        <v>21.20000076293945</v>
       </c>
       <c r="B85" t="n">
-        <v>12.98769378662109</v>
+        <v>22.51614570617676</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>23.01665115356445</v>
+        <v>29.79999923706055</v>
       </c>
       <c r="B86" t="n">
-        <v>23.78866577148438</v>
+        <v>36.83114624023438</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>24.87757110595703</v>
+        <v>16.56746101379395</v>
       </c>
       <c r="B87" t="n">
-        <v>22.43568801879883</v>
+        <v>12.10646057128906</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>21.82539749145508</v>
+        <v>22.29999923706055</v>
       </c>
       <c r="B88" t="n">
-        <v>25.04704475402832</v>
+        <v>18.8687686920166</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>12.54940700531006</v>
+        <v>8.275861740112305</v>
       </c>
       <c r="B89" t="n">
-        <v>13.81132984161377</v>
+        <v>13.07955360412598</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>14.19999980926514</v>
+        <v>38.09999847412109</v>
       </c>
       <c r="B90" t="n">
-        <v>16.66498184204102</v>
+        <v>31.42089462280273</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>23.5238094329834</v>
+        <v>23.60000038146973</v>
       </c>
       <c r="B91" t="n">
-        <v>29.8316535949707</v>
+        <v>22.80340385437012</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>9.189723014831543</v>
+        <v>22.29999923706055</v>
       </c>
       <c r="B92" t="n">
-        <v>10.29780769348145</v>
+        <v>15.42011070251465</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>19.39275169372559</v>
+        <v>0.800000011920929</v>
       </c>
       <c r="B93" t="n">
-        <v>21.33867835998535</v>
+        <v>24.89304161071777</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>54.29999923706055</v>
+        <v>24.38785552978516</v>
       </c>
       <c r="B94" t="n">
-        <v>53.11330413818359</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="n">
-        <v>18.31537628173828</v>
-      </c>
-      <c r="B95" t="n">
-        <v>15.34583854675293</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="n">
-        <v>69.63761138916016</v>
-      </c>
-      <c r="B96" t="n">
-        <v>63.34907913208008</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="n">
-        <v>14.6245059967041</v>
-      </c>
-      <c r="B97" t="n">
-        <v>18.15736389160156</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="n">
-        <v>23.10000038146973</v>
-      </c>
-      <c r="B98" t="n">
-        <v>22.5897331237793</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="n">
-        <v>21.05778694152832</v>
-      </c>
-      <c r="B99" t="n">
-        <v>21.0679874420166</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="n">
-        <v>27.18253898620605</v>
-      </c>
-      <c r="B100" t="n">
-        <v>23.13236236572266</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="n">
-        <v>41.20000076293945</v>
-      </c>
-      <c r="B101" t="n">
-        <v>35.95446395874023</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="n">
-        <v>58.76591491699219</v>
-      </c>
-      <c r="B102" t="n">
-        <v>62.40876007080078</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="n">
-        <v>13.32027435302734</v>
-      </c>
-      <c r="B103" t="n">
-        <v>13.26132583618164</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="n">
-        <v>35.29999923706055</v>
-      </c>
-      <c r="B104" t="n">
-        <v>25.77575874328613</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="n">
-        <v>30.09523773193359</v>
-      </c>
-      <c r="B105" t="n">
-        <v>21.7027702331543</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="n">
-        <v>23.01665115356445</v>
-      </c>
-      <c r="B106" t="n">
-        <v>23.78866577148438</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="n">
-        <v>12.53672885894775</v>
-      </c>
-      <c r="B107" t="n">
-        <v>18.23247909545898</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="n">
-        <v>14.58333301544189</v>
-      </c>
-      <c r="B108" t="n">
-        <v>12.98769378662109</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="n">
-        <v>19.84127044677734</v>
-      </c>
-      <c r="B109" t="n">
-        <v>34.79229736328125</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="n">
-        <v>13.10000038146973</v>
-      </c>
-      <c r="B110" t="n">
-        <v>14.1387882232666</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="n">
-        <v>24.38785552978516</v>
-      </c>
-      <c r="B111" t="n">
-        <v>20.2017765045166</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="n">
-        <v>19.84127044677734</v>
-      </c>
-      <c r="B112" t="n">
-        <v>38.66726303100586</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="n">
-        <v>32.85714340209961</v>
-      </c>
-      <c r="B113" t="n">
-        <v>25.54685020446777</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="n">
-        <v>57.09999847412109</v>
-      </c>
-      <c r="B114" t="n">
-        <v>51.58207702636719</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="B115" t="n">
-        <v>14.6810359954834</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="n">
-        <v>18.65079307556152</v>
-      </c>
-      <c r="B116" t="n">
-        <v>19.9176139831543</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="n">
-        <v>14.20176315307617</v>
-      </c>
-      <c r="B117" t="n">
-        <v>17.74725151062012</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="n">
-        <v>35.20000076293945</v>
-      </c>
-      <c r="B118" t="n">
-        <v>30.87546920776367</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="n">
-        <v>34.70000076293945</v>
-      </c>
-      <c r="B119" t="n">
-        <v>20.50998878479004</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="n">
-        <v>22.09523773193359</v>
-      </c>
-      <c r="B120" t="n">
-        <v>29.70965957641602</v>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="n">
-        <v>19.84127044677734</v>
-      </c>
-      <c r="B121" t="n">
-        <v>19.06040000915527</v>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="n">
-        <v>11.43984222412109</v>
-      </c>
-      <c r="B122" t="n">
-        <v>12.80019092559814</v>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="n">
-        <v>35.5</v>
-      </c>
-      <c r="B123" t="n">
-        <v>25.57015800476074</v>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="n">
-        <v>1.469147920608521</v>
-      </c>
-      <c r="B124" t="n">
-        <v>16.46575164794922</v>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="B125" t="n">
-        <v>11.33365058898926</v>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="n">
-        <v>32.22331237792969</v>
-      </c>
-      <c r="B126" t="n">
-        <v>31.80102920532227</v>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="n">
-        <v>19.0476188659668</v>
-      </c>
-      <c r="B127" t="n">
-        <v>33.10574340820312</v>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="n">
-        <v>11.4285717010498</v>
-      </c>
-      <c r="B128" t="n">
-        <v>10.54123592376709</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="n">
-        <v>26.44466209411621</v>
-      </c>
-      <c r="B129" t="n">
-        <v>30.38520050048828</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="n">
-        <v>31.80952453613281</v>
-      </c>
-      <c r="B130" t="n">
-        <v>22.14044570922852</v>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="n">
-        <v>39.17727661132812</v>
-      </c>
-      <c r="B131" t="n">
-        <v>43.33182907104492</v>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="n">
-        <v>12.74703598022461</v>
-      </c>
-      <c r="B132" t="n">
-        <v>16.27081489562988</v>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="n">
-        <v>95.23809814453125</v>
-      </c>
-      <c r="B133" t="n">
-        <v>95.10498046875</v>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="n">
-        <v>24.58374214172363</v>
-      </c>
-      <c r="B134" t="n">
-        <v>29.10256767272949</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="n">
-        <v>19.19686508178711</v>
-      </c>
-      <c r="B135" t="n">
-        <v>26.4616527557373</v>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="n">
-        <v>9.486166000366211</v>
-      </c>
-      <c r="B136" t="n">
-        <v>8.67641544342041</v>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="n">
-        <v>121.9246063232422</v>
-      </c>
-      <c r="B137" t="n">
-        <v>117.6722030639648</v>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="n">
-        <v>38.19047546386719</v>
-      </c>
-      <c r="B138" t="n">
-        <v>22.97066116333008</v>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="n">
-        <v>11.65524005889893</v>
-      </c>
-      <c r="B139" t="n">
-        <v>18.15031051635742</v>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="n">
-        <v>29.79999923706055</v>
-      </c>
-      <c r="B140" t="n">
-        <v>28.82135200500488</v>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="n">
-        <v>16.56746101379395</v>
-      </c>
-      <c r="B141" t="n">
-        <v>11.78037452697754</v>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="n">
-        <v>59.70000076293945</v>
-      </c>
-      <c r="B142" t="n">
-        <v>58.4210205078125</v>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="n">
-        <v>8.275861740112305</v>
-      </c>
-      <c r="B143" t="n">
-        <v>8.207772254943848</v>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="n">
-        <v>38.09999847412109</v>
-      </c>
-      <c r="B144" t="n">
-        <v>35.44504165649414</v>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="n">
-        <v>37.59999847412109</v>
-      </c>
-      <c r="B145" t="n">
-        <v>26.75459671020508</v>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="n">
-        <v>24.38785552978516</v>
-      </c>
-      <c r="B146" t="n">
-        <v>20.2017765045166</v>
+        <v>25.13603401184082</v>
       </c>
     </row>
   </sheetData>
